--- a/samples/issue_list_template.xlsx
+++ b/samples/issue_list_template.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026/09/23</t>
+          <t>2026/09/25</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
